--- a/outputs/week2_excel/301581_黄山谷捷_三表抽取.xlsx
+++ b/outputs/week2_excel/301581_黄山谷捷_三表抽取.xlsx
@@ -1976,13 +1976,13 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>张松满</t>
+          <t>孙国奉</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>162.5</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -2056,13 +2056,13 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>孙国奉</t>
+          <t>张松满</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>162.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2596,15 +2596,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -2616,7 +2612,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2634,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2752,11 +2748,15 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3246,13 +3246,13 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -3288,13 +3288,13 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -3330,13 +3330,13 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>1584.0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -3372,15 +3372,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -3392,7 +3388,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3414,11 +3410,15 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3452,13 +3452,13 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>7412.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -3536,15 +3536,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
@@ -3556,7 +3552,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3578,11 +3574,15 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -3692,15 +3692,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -3712,7 +3708,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3730,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -3772,11 +3768,15 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -4144,11 +4144,15 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -4160,7 +4164,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4182,15 +4186,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>10377.0</t>
-        </is>
-      </c>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -5102,14 +5102,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
@@ -5118,7 +5126,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5186,22 +5194,14 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5232,14 +5232,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
@@ -5248,7 +5256,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5270,22 +5278,14 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5316,20 +5316,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="J107" t="inlineStr"/>
@@ -5362,23 +5362,23 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -5412,22 +5412,26 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
@@ -5436,7 +5440,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5458,26 +5462,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>罗世兵</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>408.0</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5508,22 +5508,26 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -5532,7 +5536,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5554,20 +5558,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="J112" t="inlineStr"/>
@@ -5600,23 +5604,23 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>17952.0</t>
+          <t>408.0</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -5650,26 +5654,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5700,22 +5700,30 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>86.5984</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>86.5984</t>
-        </is>
-      </c>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
@@ -5724,7 +5732,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5746,20 +5754,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J116" t="inlineStr"/>
@@ -5838,20 +5846,20 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J118" t="inlineStr"/>
@@ -5884,22 +5892,30 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>10.1093</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>10.1093</t>
-        </is>
-      </c>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -5908,7 +5924,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5930,30 +5946,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>1680.0</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
@@ -5962,7 +5970,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5984,20 +5992,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -6030,27 +6038,27 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
           <t>360.0</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>720.0</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -6084,20 +6092,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -6130,20 +6138,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -6176,20 +6184,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>59.4667</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>59.4667</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -6222,30 +6230,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6276,20 +6276,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>陆民</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -7300,11 +7300,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7324,7 +7320,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -7362,7 +7358,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -7400,7 +7396,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -7416,7 +7412,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7434,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>陆民</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -7452,7 +7448,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -7700,7 +7700,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -7776,7 +7776,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -8004,7 +8004,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -8042,11 +8042,15 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
@@ -8056,11 +8060,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8080,15 +8080,11 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
@@ -8098,7 +8094,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr"/>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -8472,15 +8472,11 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>吴功友(王金林代持)</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
+      <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
@@ -8492,7 +8488,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8514,7 +8510,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -8552,13 +8548,13 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>吴功友(王金林代持)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="G181" t="inlineStr"/>
@@ -8594,11 +8590,15 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8674,20 +8674,20 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="J184" t="inlineStr"/>
@@ -8762,20 +8762,20 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="J186" t="inlineStr"/>
@@ -8808,20 +8808,20 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="J187" t="inlineStr"/>
@@ -8896,20 +8896,20 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="J189" t="inlineStr"/>
@@ -8942,20 +8942,20 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="J190" t="inlineStr"/>
@@ -8988,20 +8988,20 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>策星银河</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="J191" t="inlineStr"/>
@@ -9429,7 +9429,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T10:04:41.033551</t>
+          <t>生成时间: 2026-06-12T14:44:15.802401</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/301581_黄山谷捷_三表抽取.xlsx
+++ b/outputs/week2_excel/301581_黄山谷捷_三表抽取.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -452,7 +452,10 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -488,6 +491,21 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>事件类型</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>增资后总股本(万股)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>认购占比</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>原文证据</t>
         </is>
       </c>
@@ -513,6 +531,16 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>2012年4月11日，黄山市供销社出具《关于同意投资昆山谷捷项目的批复》（黄供财[2012]22号），同意设立谷捷有限。2012年5月28日，谷捷有限股东昆山谷捷作出股东决定，同意由昆山谷捷出资1,000万元设立谷捷有限。2012年6月12日，安徽天正达会计师事务所出具《验资报告》，确认谷捷有限已收到昆山谷捷缴纳的注册资本1,000万元，出资方式为货币。设立时昆山谷捷持股100%。</t>
         </is>
       </c>
@@ -538,6 +566,16 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>股权转让</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>78.00%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>2020年12月30日，黄山市供销社、黄山供销集团出具批复，同意昆山谷捷将其所持谷捷有限78%、11%、11%的股权以零对价分别转让给黄山供销集团、张俊武、周斌。2021年4月3日，昆山谷捷分别与黄山供销集团、张俊武、周斌签署了股权转让相关协议。本次股权转让系同一股权结构下的公司架构调整，转让价格为0元。转让后股权结构：黄山供销集团78.00%、张俊武11.00%、周斌11.00%。</t>
         </is>
       </c>
@@ -563,6 +601,16 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>股权转让</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>11.00%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>2020年12月30日，黄山市供销社、黄山供销集团出具批复，同意昆山谷捷将其所持谷捷有限78%、11%、11%的股权以零对价分别转让给黄山供销集团、张俊武、周斌。2021年4月3日，昆山谷捷分别与黄山供销集团、张俊武、周斌签署了股权转让相关协议。本次股权转让系同一股权结构下的公司架构调整，转让价格为0元。转让后股权结构：黄山供销集团78.00%、张俊武11.00%、周斌11.00%。</t>
         </is>
       </c>
@@ -588,6 +636,16 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>股权转让</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>11.00%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>2020年12月30日，黄山市供销社、黄山供销集团出具批复，同意昆山谷捷将其所持谷捷有限78%、11%、11%的股权以零对价分别转让给黄山供销集团、张俊武、周斌。2021年4月3日，昆山谷捷分别与黄山供销集团、张俊武、周斌签署了股权转让相关协议。本次股权转让系同一股权结构下的公司架构调整，转让价格为0元。转让后股权结构：黄山供销集团78.00%、张俊武11.00%、周斌11.00%。</t>
         </is>
       </c>
@@ -610,6 +668,16 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>78.00%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>2020年12月24日，谷捷有限及昆山谷捷召开股东会，同意谷捷有限吸收合并昆山谷捷。2021年4月7日，谷捷有限召开股东会，吸收合并后注册资本变更为1,200万元（黄山供销集团936万、张俊武132万、周斌132万）。本次吸收合并系同一股权结构下的公司架构调整。截至2021年3月31日，昆山谷捷净资产账面价值380.94万元，谷捷有限净资产账面价值2,912.30万元，评估价值9,651.75万元。</t>
         </is>
       </c>
@@ -632,6 +700,16 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>11.00%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>2020年12月24日，谷捷有限及昆山谷捷召开股东会，同意谷捷有限吸收合并昆山谷捷。2021年4月7日，谷捷有限召开股东会，吸收合并后注册资本变更为1,200万元（黄山供销集团936万、张俊武132万、周斌132万）。本次吸收合并系同一股权结构下的公司架构调整。截至2021年3月31日，昆山谷捷净资产账面价值380.94万元，谷捷有限净资产账面价值2,912.30万元，评估价值9,651.75万元。</t>
         </is>
       </c>
@@ -654,6 +732,16 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>11.00%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>2020年12月24日，谷捷有限及昆山谷捷召开股东会，同意谷捷有限吸收合并昆山谷捷。2021年4月7日，谷捷有限召开股东会，吸收合并后注册资本变更为1,200万元（黄山供销集团936万、张俊武132万、周斌132万）。本次吸收合并系同一股权结构下的公司架构调整。截至2021年3月31日，昆山谷捷净资产账面价值380.94万元，谷捷有限净资产账面价值2,912.30万元，评估价值9,651.75万元。</t>
         </is>
       </c>
@@ -682,6 +770,16 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>27.00%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>2021年9月18日，赛格高技术、上汽科技与黄山供销集团、张俊武、周斌及谷捷有限签署《增资协议》，约定谷捷有限增加注册资本514.2857万元，其中赛格高技术认缴462.8571万元、上汽科技认缴51.4286万元，增资价格为22.42元/注册资本，出资方式为货币。增资后：黄山供销集团54.60%、赛格高技术27.00%、张俊武7.70%、周斌7.70%、上汽科技3.00%。</t>
         </is>
       </c>
@@ -710,6 +808,16 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3.00%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>2021年9月18日，赛格高技术、上汽科技与黄山供销集团、张俊武、周斌及谷捷有限签署《增资协议》，约定谷捷有限增加注册资本514.2857万元，其中赛格高技术认缴462.8571万元、上汽科技认缴51.4286万元，增资价格为22.42元/注册资本，出资方式为货币。增资后：黄山供销集团54.60%、赛格高技术27.00%、张俊武7.70%、周斌7.70%、上汽科技3.00%。</t>
         </is>
       </c>
@@ -738,6 +846,16 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>2022年5月20日，谷捷有限召开股东会，同意注册资本由1,714.2857万元增至1,804.5113万元，新增注册资本90.2256万元由员工持股平台黄山佳捷全额认缴。增资价格为23.55元/注册资本，出资方式为货币。增资后：黄山供销集团51.87%、赛格高技术25.65%、张俊武7.315%、周斌7.315%、黄山佳捷5.00%、上汽科技2.85%。</t>
         </is>
       </c>
@@ -760,6 +878,16 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>51.87%</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>2022年8月24日，谷捷有限召开股东会，同意以截至2022年5月31日经审计的净资产20,152.51万元按1:0.29773比例折成6,000万股，每股面值1元，净资产余额14,152.51万元转为资本公积，整体变更后各股东持股比例保持不变。2022年9月13日取得换发营业执照。</t>
         </is>
       </c>
@@ -782,6 +910,16 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25.65%</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>2022年8月24日，谷捷有限召开股东会，同意以截至2022年5月31日经审计的净资产20,152.51万元按1:0.29773比例折成6,000万股，每股面值1元，净资产余额14,152.51万元转为资本公积，整体变更后各股东持股比例保持不变。2022年9月13日取得换发营业执照。</t>
         </is>
       </c>
@@ -804,6 +942,16 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7.315%</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>2022年8月24日，谷捷有限召开股东会，同意以截至2022年5月31日经审计的净资产20,152.51万元按1:0.29773比例折成6,000万股，每股面值1元，净资产余额14,152.51万元转为资本公积，整体变更后各股东持股比例保持不变。2022年9月13日取得换发营业执照。</t>
         </is>
       </c>
@@ -826,6 +974,16 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7.315%</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>2022年8月24日，谷捷有限召开股东会，同意以截至2022年5月31日经审计的净资产20,152.51万元按1:0.29773比例折成6,000万股，每股面值1元，净资产余额14,152.51万元转为资本公积，整体变更后各股东持股比例保持不变。2022年9月13日取得换发营业执照。</t>
         </is>
       </c>
@@ -848,6 +1006,16 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>2022年8月24日，谷捷有限召开股东会，同意以截至2022年5月31日经审计的净资产20,152.51万元按1:0.29773比例折成6,000万股，每股面值1元，净资产余额14,152.51万元转为资本公积，整体变更后各股东持股比例保持不变。2022年9月13日取得换发营业执照。</t>
         </is>
       </c>
@@ -869,6 +1037,16 @@
         </is>
       </c>
       <c r="G17" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2.85%</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>2022年8月24日，谷捷有限召开股东会，同意以截至2022年5月31日经审计的净资产20,152.51万元按1:0.29773比例折成6,000万股，每股面值1元，净资产余额14,152.51万元转为资本公积，整体变更后各股东持股比例保持不变。2022年9月13日取得换发营业执照。</t>
         </is>
@@ -885,7 +1063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -897,7 +1075,10 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -948,6 +1129,21 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>快照序号</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>股东类型</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>原始创始人</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>原文证据</t>
         </is>
       </c>
@@ -983,6 +1179,21 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>产业资本</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>2012年4月11日，黄山市供销社出具《关于同意投资昆山谷捷项目的批复》（黄供财[2012]22号），同意设立谷捷有限。2012年5月28日，谷捷有限股东昆山谷捷作出股东决定，同意由昆山谷捷出资1,000万元设立谷捷有限。2012年6月12日，安徽天正达会计师事务所出具《验资报告》，确认谷捷有限已收到昆山谷捷缴纳的注册资本1,000万元，出资方式为货币。设立时昆山谷捷持股100%。</t>
         </is>
       </c>
@@ -1015,6 +1226,21 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>政府基金</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>2020年12月30日，黄山市供销社、黄山供销集团出具批复，同意昆山谷捷将其所持谷捷有限78%、11%、11%的股权以零对价分别转让给黄山供销集团、张俊武、周斌。2021年4月3日，昆山谷捷分别与黄山供销集团、张俊武、周斌签署了股权转让相关协议。本次股权转让系同一股权结构下的公司架构调整，转让价格为0元。转让后股权结构：黄山供销集团78.00%、张俊武11.00%、周斌11.00%。</t>
         </is>
       </c>
@@ -1047,6 +1273,21 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>2020年12月30日，黄山市供销社、黄山供销集团出具批复，同意昆山谷捷将其所持谷捷有限78%、11%、11%的股权以零对价分别转让给黄山供销集团、张俊武、周斌。2021年4月3日，昆山谷捷分别与黄山供销集团、张俊武、周斌签署了股权转让相关协议。本次股权转让系同一股权结构下的公司架构调整，转让价格为0元。转让后股权结构：黄山供销集团78.00%、张俊武11.00%、周斌11.00%。</t>
         </is>
       </c>
@@ -1079,6 +1320,21 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>2020年12月30日，黄山市供销社、黄山供销集团出具批复，同意昆山谷捷将其所持谷捷有限78%、11%、11%的股权以零对价分别转让给黄山供销集团、张俊武、周斌。2021年4月3日，昆山谷捷分别与黄山供销集团、张俊武、周斌签署了股权转让相关协议。本次股权转让系同一股权结构下的公司架构调整，转让价格为0元。转让后股权结构：黄山供销集团78.00%、张俊武11.00%、周斌11.00%。</t>
         </is>
       </c>
@@ -1111,6 +1367,21 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>政府基金</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>2020年12月24日，谷捷有限及昆山谷捷召开股东会，同意谷捷有限吸收合并昆山谷捷。2021年4月7日，谷捷有限召开股东会，吸收合并后注册资本变更为1,200万元（黄山供销集团936万、张俊武132万、周斌132万）。本次吸收合并系同一股权结构下的公司架构调整。截至2021年3月31日，昆山谷捷净资产账面价值380.94万元，谷捷有限净资产账面价值2,912.30万元，评估价值9,651.75万元。</t>
         </is>
       </c>
@@ -1143,6 +1414,21 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>2020年12月24日，谷捷有限及昆山谷捷召开股东会，同意谷捷有限吸收合并昆山谷捷。2021年4月7日，谷捷有限召开股东会，吸收合并后注册资本变更为1,200万元（黄山供销集团936万、张俊武132万、周斌132万）。本次吸收合并系同一股权结构下的公司架构调整。截至2021年3月31日，昆山谷捷净资产账面价值380.94万元，谷捷有限净资产账面价值2,912.30万元，评估价值9,651.75万元。</t>
         </is>
       </c>
@@ -1175,6 +1461,21 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>2020年12月24日，谷捷有限及昆山谷捷召开股东会，同意谷捷有限吸收合并昆山谷捷。2021年4月7日，谷捷有限召开股东会，吸收合并后注册资本变更为1,200万元（黄山供销集团936万、张俊武132万、周斌132万）。本次吸收合并系同一股权结构下的公司架构调整。截至2021年3月31日，昆山谷捷净资产账面价值380.94万元，谷捷有限净资产账面价值2,912.30万元，评估价值9,651.75万元。</t>
         </is>
       </c>
@@ -1213,6 +1514,21 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>产业资本</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>2021年9月18日，赛格高技术、上汽科技与黄山供销集团、张俊武、周斌及谷捷有限签署《增资协议》，约定谷捷有限增加注册资本514.2857万元，其中赛格高技术认缴462.8571万元、上汽科技认缴51.4286万元，增资价格为22.42元/注册资本，出资方式为货币。增资后：黄山供销集团54.60%、赛格高技术27.00%、张俊武7.70%、周斌7.70%、上汽科技3.00%。</t>
         </is>
       </c>
@@ -1251,6 +1567,21 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>产业资本</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>2021年9月18日，赛格高技术、上汽科技与黄山供销集团、张俊武、周斌及谷捷有限签署《增资协议》，约定谷捷有限增加注册资本514.2857万元，其中赛格高技术认缴462.8571万元、上汽科技认缴51.4286万元，增资价格为22.42元/注册资本，出资方式为货币。增资后：黄山供销集团54.60%、赛格高技术27.00%、张俊武7.70%、周斌7.70%、上汽科技3.00%。</t>
         </is>
       </c>
@@ -1289,6 +1620,21 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>2022年5月20日，谷捷有限召开股东会，同意注册资本由1,714.2857万元增至1,804.5113万元，新增注册资本90.2256万元由员工持股平台黄山佳捷全额认缴。增资价格为23.55元/注册资本，出资方式为货币。增资后：黄山供销集团51.87%、赛格高技术25.65%、张俊武7.315%、周斌7.315%、黄山佳捷5.00%、上汽科技2.85%。</t>
         </is>
       </c>
@@ -1321,6 +1667,21 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>政府基金</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
           <t>2022年8月24日，谷捷有限召开股东会，同意以截至2022年5月31日经审计的净资产20,152.51万元按1:0.29773比例折成6,000万股，每股面值1元，净资产余额14,152.51万元转为资本公积，整体变更后各股东持股比例保持不变。2022年9月13日取得换发营业执照。</t>
         </is>
       </c>
@@ -1353,6 +1714,21 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>产业资本</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>2022年8月24日，谷捷有限召开股东会，同意以截至2022年5月31日经审计的净资产20,152.51万元按1:0.29773比例折成6,000万股，每股面值1元，净资产余额14,152.51万元转为资本公积，整体变更后各股东持股比例保持不变。2022年9月13日取得换发营业执照。</t>
         </is>
       </c>
@@ -1385,6 +1761,21 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
           <t>2022年8月24日，谷捷有限召开股东会，同意以截至2022年5月31日经审计的净资产20,152.51万元按1:0.29773比例折成6,000万股，每股面值1元，净资产余额14,152.51万元转为资本公积，整体变更后各股东持股比例保持不变。2022年9月13日取得换发营业执照。</t>
         </is>
       </c>
@@ -1417,6 +1808,21 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
           <t>2022年8月24日，谷捷有限召开股东会，同意以截至2022年5月31日经审计的净资产20,152.51万元按1:0.29773比例折成6,000万股，每股面值1元，净资产余额14,152.51万元转为资本公积，整体变更后各股东持股比例保持不变。2022年9月13日取得换发营业执照。</t>
         </is>
       </c>
@@ -1449,6 +1855,21 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
           <t>2022年8月24日，谷捷有限召开股东会，同意以截至2022年5月31日经审计的净资产20,152.51万元按1:0.29773比例折成6,000万股，每股面值1元，净资产余额14,152.51万元转为资本公积，整体变更后各股东持股比例保持不变。2022年9月13日取得换发营业执照。</t>
         </is>
       </c>
@@ -1480,6 +1901,21 @@
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>产业资本</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>2022年8月24日，谷捷有限召开股东会，同意以截至2022年5月31日经审计的净资产20,152.51万元按1:0.29773比例折成6,000万股，每股面值1元，净资产余额14,152.51万元转为资本公积，整体变更后各股东持股比例保持不变。2022年9月13日取得换发营业执照。</t>
         </is>
@@ -1496,7 +1932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L203"/>
+  <dimension ref="A1:L211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1670,100 +2106,84 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>evidence_text</t>
+          <t>event_context</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>str(min=20)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>source_page</t>
+          <t>post_event_total_shares</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>snapshot_date</t>
+          <t>post_event_total_capital</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>str(YYYY-MM-DD)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>snapshot_type</t>
+          <t>payment_method</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>total_shares</t>
+          <t>subscription_ratio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>float|null</t>
+          <t>str|null</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1771,20 +2191,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>total_capital</t>
+          <t>evidence_text</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>float|null</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>str(min=20)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1794,7 +2218,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>shareholder_name</t>
+          <t>source_page</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1816,15 +2240,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>shares_held</t>
+          <t>snapshot_date</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>float|null</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>str(YYYY-MM-DD)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1834,15 +2262,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>capital_contribution</t>
+          <t>snapshot_type</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>float|null</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1852,12 +2284,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>shareholding_ratio</t>
+          <t>total_shares</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>str|null</t>
+          <t>float|null</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1870,433 +2302,269 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>total_capital</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>shareholder_name</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>shares_held</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>capital_contribution</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>shareholding_ratio</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>str|null</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>snapshot_order</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>int|null</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>shareholder_type_detail</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>is_original_founder</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>yes/no/unknown</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>evidence_text</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>str(min=20)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Cross-Check 结果（相邻时点股本追踪 + 认缴存量对应）</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>公司</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
+      <c r="B32" s="1" t="inlineStr">
         <is>
           <t>上一时点</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>当前时点</t>
         </is>
       </c>
-      <c r="D24" s="1" t="inlineStr">
+      <c r="D32" s="1" t="inlineStr">
         <is>
           <t>股东名称</t>
         </is>
       </c>
-      <c r="E24" s="1" t="inlineStr">
+      <c r="E32" s="1" t="inlineStr">
         <is>
           <t>上一时点持股数
 (万股)</t>
         </is>
       </c>
-      <c r="F24" s="1" t="inlineStr">
+      <c r="F32" s="1" t="inlineStr">
         <is>
           <t>上一时点出资额
 (万元注册资本)</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
+      <c r="G32" s="1" t="inlineStr">
         <is>
           <t>本次认缴/变化
 (万股)</t>
         </is>
       </c>
-      <c r="H24" s="1" t="inlineStr">
+      <c r="H32" s="1" t="inlineStr">
         <is>
           <t>预期变更后
 持股数(万股)</t>
         </is>
       </c>
-      <c r="I24" s="1" t="inlineStr">
+      <c r="I32" s="1" t="inlineStr">
         <is>
           <t>PDF披露
 持股数(万股)</t>
         </is>
       </c>
-      <c r="J24" s="1" t="inlineStr">
+      <c r="J32" s="1" t="inlineStr">
         <is>
           <t>差额(万股)</t>
         </is>
       </c>
-      <c r="K24" s="1" t="inlineStr">
+      <c r="K32" s="1" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="L24" s="1" t="inlineStr">
+      <c r="L32" s="1" t="inlineStr">
         <is>
           <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>001282_三联锻造</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2004-06-18</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2014-05</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>孙国奉</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>175.0</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>001282_三联锻造</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2004-06-18</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2014-05</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>孙国敏</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>162.5</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>001282_三联锻造</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2004-06-18</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2014-05</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>张松满</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>162.5</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>武汉力源信息技术股份有限公司</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>深圳市云汉电子有限公司</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>刘云锋</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>301563_云汉芯城</t>
+          <t>001282_三联锻造</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2004-06-18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>孙国奉</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>175.0</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -2306,35 +2574,35 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>301563_云汉芯城</t>
+          <t>001282_三联锻造</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2004-06-18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>张松满</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>162.5</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -2344,35 +2612,35 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>301563_云汉芯城</t>
+          <t>001282_三联锻造</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2004-06-18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>孙国敏</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>162.5</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -2384,7 +2652,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2396,17 +2664,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -2434,21 +2702,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -2472,21 +2744,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -2498,7 +2774,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2510,17 +2786,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2536,7 +2812,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2548,17 +2824,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2586,17 +2862,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2612,7 +2888,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2624,17 +2900,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2662,17 +2938,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2688,7 +2964,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2700,17 +2976,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2726,7 +3002,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2738,25 +3014,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -2768,7 +3040,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2780,17 +3052,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2806,7 +3078,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2818,17 +3090,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2844,7 +3116,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2856,17 +3128,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2894,17 +3166,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2932,17 +3204,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2958,7 +3230,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2970,21 +3242,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -2996,7 +3272,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3008,17 +3284,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -3046,17 +3322,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -3084,17 +3360,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3110,7 +3386,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3122,17 +3398,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3160,17 +3436,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3186,7 +3462,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3484,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3224,7 +3500,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3236,25 +3512,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>7412.0</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -3266,7 +3538,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3278,25 +3550,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -3320,25 +3588,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>1584.0</t>
-        </is>
-      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -3350,7 +3614,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3362,17 +3626,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -3400,25 +3664,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -3430,7 +3690,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3442,25 +3702,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -3472,7 +3728,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3484,25 +3740,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -3514,7 +3766,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3526,17 +3778,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2020-05-28</t>
+          <t>2015-12-03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3552,7 +3804,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3564,25 +3816,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>2018-06-28</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
           <t>2020-05-28</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -3594,7 +3842,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3606,21 +3854,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>2018-06-28</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
           <t>2020-05-28</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -3632,33 +3884,37 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
@@ -3670,33 +3926,37 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>7412.0</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -3708,33 +3968,37 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -3746,35 +4010,35 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -3795,26 +4059,30 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1584.0</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -3824,31 +4092,39 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -3858,27 +4134,31 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -3892,27 +4172,31 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -3928,7 +4212,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3940,12 +4224,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3966,7 +4250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3978,17 +4262,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -4016,17 +4300,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -4054,21 +4338,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -4092,25 +4380,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>1153.0</t>
-        </is>
-      </c>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
@@ -4120,11 +4404,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4134,25 +4414,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>10377.0</t>
-        </is>
-      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -4162,11 +4438,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4176,17 +4448,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -4200,11 +4472,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4214,17 +4482,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4240,7 +4508,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4252,12 +4520,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4278,7 +4546,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4290,12 +4558,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4328,12 +4596,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4366,25 +4634,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
@@ -4394,7 +4658,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4404,21 +4672,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
           <t>2022-05-26</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>2022-09-13</t>
-        </is>
-      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1153.0</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -4430,49 +4702,37 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-05-26</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>6999.972</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>-0.028</t>
-        </is>
-      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4480,49 +4740,41 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-05-26</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>2999.988</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>-0.012</t>
-        </is>
-      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4530,49 +4782,37 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>1499.994</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>-0.006</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4580,49 +4820,37 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>10000.0027</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>10000.0</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>0.0027</t>
-        </is>
-      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4630,49 +4858,37 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>10000.0027</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>10000.0</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>0.0027</t>
-        </is>
-      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4680,99 +4896,75 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>148.6667</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>5000.0031</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>0.0031</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>price×shares vs amount diff=0.0%</t>
-        </is>
-      </c>
+      <c r="L94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>3000.0012</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>0.0012</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4780,49 +4972,37 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>86.5984</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>2912.5034</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>2912.5</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>0.0034</t>
-        </is>
-      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4830,7 +5010,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4843,34 +5023,34 @@
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2000.0019</t>
+          <t>6999.972</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>7000.0</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>0.0019</t>
+          <t>-0.028</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -4893,34 +5073,34 @@
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1747.5007</t>
+          <t>2999.988</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1747.5</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>0.0007</t>
+          <t>-0.012</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -4943,34 +5123,34 @@
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>999.9993</t>
+          <t>1499.994</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1500.0</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>-0.0007</t>
+          <t>-0.006</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -4998,29 +5178,29 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>999.9993</t>
+          <t>10000.0027</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>-0.0007</t>
+          <t>0.0027</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -5048,29 +5228,29 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>339.999</t>
+          <t>10000.0027</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>340.0</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>0.0027</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -5090,35 +5270,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>5000.0031</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr"/>
+          <t>5000.0</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>0.0031</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5126,7 +5310,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5136,35 +5320,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>3000.0012</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr"/>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>0.0012</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5172,7 +5360,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5182,27 +5370,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2912.5034</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2912.5</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>0.0034</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5210,7 +5410,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5220,35 +5420,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr"/>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2000.0019</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr"/>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>0.0019</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5256,7 +5460,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5266,27 +5470,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1747.5007</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1747.5</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>0.0007</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5294,7 +5510,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5304,35 +5520,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>999.9993</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr"/>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5340,7 +5560,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5350,39 +5570,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2020-09-09</t>
-        </is>
-      </c>
+      <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+          <t>999.9993</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5390,7 +5610,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5400,39 +5620,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2020-09-09</t>
-        </is>
-      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
+          <t>339.999</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>340.0</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>-0.001</t>
+        </is>
+      </c>
       <c r="K109" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5440,7 +5660,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5452,30 +5672,30 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J110" t="inlineStr"/>
@@ -5498,36 +5718,32 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>17952.0</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -5536,7 +5752,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5548,32 +5764,24 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -5582,7 +5790,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5594,36 +5802,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D113" t="inlineStr">
         <is>
           <t>罗世兵</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>204.0</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>408.0</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
@@ -5632,7 +5836,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5644,32 +5848,24 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
@@ -5678,7 +5874,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5690,40 +5886,32 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>1680.0</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
@@ -5732,7 +5920,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5744,32 +5932,36 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
@@ -5778,7 +5970,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5790,30 +5982,30 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="J117" t="inlineStr"/>
@@ -5836,32 +6028,36 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
@@ -5870,7 +6066,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5882,40 +6078,32 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>720.0</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -5924,7 +6112,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5936,32 +6124,36 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
@@ -5970,7 +6162,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5982,30 +6174,30 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -6028,37 +6220,33 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -6092,20 +6280,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -6138,20 +6326,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -6184,20 +6372,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -6230,20 +6418,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -6276,20 +6464,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -6310,39 +6498,43 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司 (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6350,7 +6542,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6360,39 +6552,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6400,7 +6588,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6410,39 +6598,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6450,7 +6634,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6460,39 +6644,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>罗世兵 (认缴→存量)</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6500,7 +6680,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6510,39 +6690,43 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6550,7 +6734,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6560,39 +6744,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6600,7 +6780,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6610,39 +6790,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙) (认缴→存量)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6650,7 +6826,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6660,7 +6836,11 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C135" t="inlineStr">
         <is>
           <t>2022-12-19</t>
@@ -6668,31 +6848,31 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6700,7 +6880,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6713,29 +6893,29 @@
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙) (认缴→存量)</t>
+          <t>上海泽升贸易有限公司 (认缴→存量)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -6763,29 +6943,29 @@
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙) (认缴→存量)</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -6813,29 +6993,29 @@
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙) (认缴→存量)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -6863,29 +7043,29 @@
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙) (认缴→存量)</t>
+          <t>罗世兵 (认缴→存量)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -6913,29 +7093,29 @@
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -6963,29 +7143,29 @@
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -7013,29 +7193,29 @@
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -7068,24 +7248,24 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司 (认缴→存量)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -7118,24 +7298,24 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙) (认缴→存量)</t>
+          <t>上海联炻企业管理中心(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -7157,30 +7337,42 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K145" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7188,37 +7380,49 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K146" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7226,37 +7430,49 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K147" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7264,71 +7480,99 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>陆民</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K148" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K149" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7336,37 +7580,49 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K150" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7374,37 +7630,49 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>深圳市达晨财智创业投资管理有限公司 (认缴→存量)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K151" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7412,37 +7680,49 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K152" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7450,7 +7730,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
@@ -7472,7 +7752,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -7510,7 +7790,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -7548,7 +7828,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -7564,7 +7844,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7866,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -7609,22 +7889,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>陆民</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -7638,31 +7918,27 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -7685,22 +7961,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -7716,29 +7992,29 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -7754,29 +8030,29 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -7792,29 +8068,29 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -7837,22 +8113,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -7875,22 +8151,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -7928,7 +8204,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -7956,17 +8232,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -7982,7 +8258,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7994,17 +8270,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -8020,7 +8296,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8032,25 +8308,21 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
@@ -8060,7 +8332,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr"/>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8070,17 +8346,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -8096,7 +8372,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8108,17 +8384,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -8146,17 +8422,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -8172,7 +8448,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8184,17 +8460,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -8210,7 +8486,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8222,17 +8498,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -8260,21 +8536,25 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
           <t>2020-02-26</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>2023-03-24</t>
-        </is>
-      </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
@@ -8284,51 +8564,35 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>盛祎等15名自然人</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>321.5</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>1739.315</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>1723.09</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>16.225</t>
-        </is>
-      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8336,29 +8600,29 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.9%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -8381,22 +8645,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>盛祎</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -8412,29 +8676,29 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>朱绶青</t>
+          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -8450,29 +8714,29 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -8488,29 +8752,29 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -8526,37 +8790,33 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>吴功友(王金林代持)</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
+      <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
@@ -8575,30 +8835,26 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
-      </c>
+      <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
@@ -8617,34 +8873,42 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>2016-12-14</t>
-        </is>
-      </c>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>牛威(罗永红代持)</t>
+          <t>盛祎等15名自然人</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>321.5</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>1739.315</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>1723.09</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>16.225</t>
+        </is>
+      </c>
       <c r="K183" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8652,44 +8916,36 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.9%</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>朱绶青</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
+      <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
+      <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
@@ -8698,37 +8954,33 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>盛祎</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
@@ -8747,37 +8999,29 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+      <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
@@ -8798,32 +9042,28 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+      <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
@@ -8832,7 +9072,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8844,23 +9084,23 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>吴功友(王金林代持)</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="G188" t="inlineStr"/>
@@ -8886,32 +9126,24 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+      <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+      <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
@@ -8932,32 +9164,24 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+      <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+      <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
@@ -8978,32 +9202,28 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>牛威(罗永红代持)</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
@@ -9012,7 +9232,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9034,22 +9254,18 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
+      <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
@@ -9058,7 +9274,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9068,7 +9284,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr"/>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C193" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9076,31 +9296,23 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司 (认缴→存量)</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9108,7 +9320,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9330,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C194" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9126,7 +9342,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>策星九天 (认缴→存量)</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -9136,21 +9352,13 @@
           <t>2345.0781</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
         <is>
           <t>2345.0781</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9158,7 +9366,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9168,7 +9376,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr"/>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C195" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9176,31 +9388,23 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>幸福一期 (认缴→存量)</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9208,7 +9412,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9422,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr"/>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C196" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9226,31 +9434,23 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>策星揽月 (认缴→存量)</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9258,7 +9458,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9468,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr"/>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C197" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9276,31 +9480,23 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>幸福二期 (认缴→存量)</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9308,7 +9504,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9318,7 +9514,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C198" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9326,31 +9526,23 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>策星银河 (认缴→存量)</t>
+          <t>策星逐日</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9358,7 +9550,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9560,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr"/>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C199" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9376,31 +9572,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>策星逐日 (认缴→存量)</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
+      <c r="F199" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9408,35 +9592,431 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>策星银河</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>中科星图股份有限公司 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
           <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="3" t="inlineStr">
-        <is>
-          <t>认缴流量: 16 条</t>
-        </is>
-      </c>
-    </row>
     <row r="202">
-      <c r="A202" s="3" t="inlineStr">
-        <is>
-          <t>股权存量: 16 条</t>
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>策星九天 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T14:44:15.802401</t>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>幸福一期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>策星揽月 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>幸福二期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>策星银河 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>策星逐日 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>认缴流量: 16 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>股权存量: 16 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>生成时间: 2026-06-12T15:16:10.987980</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A30:L30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/week2_excel/301581_黄山谷捷_三表抽取.xlsx
+++ b/outputs/week2_excel/301581_黄山谷捷_三表抽取.xlsx
@@ -2594,7 +2594,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>孙国敏</t>
+          <t>张松满</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -2612,11 +2612,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2636,7 +2632,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>张松满</t>
+          <t>孙国敏</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -2654,7 +2650,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2674,11 +2674,15 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -2690,7 +2694,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2712,15 +2716,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>深圳市云汉电子有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -3176,15 +3176,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -3196,7 +3192,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3214,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -3234,7 +3230,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3256,7 +3252,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -3272,7 +3268,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3290,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -3310,7 +3306,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3328,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -3348,7 +3344,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3370,11 +3366,15 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -3538,7 +3538,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3826,13 +3826,13 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -3868,13 +3868,13 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>7412.0</t>
+          <t>1584.0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -3910,13 +3910,13 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -3952,13 +3952,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -3994,13 +3994,13 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -4074,13 +4074,13 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -4154,15 +4154,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -4174,7 +4170,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4196,11 +4192,15 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4272,15 +4272,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -4292,7 +4288,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4314,11 +4310,15 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -4682,15 +4682,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>1153.0</t>
-        </is>
-      </c>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -4702,7 +4698,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4766,11 +4762,15 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1153.0</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4842,11 +4842,15 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
@@ -4856,11 +4860,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4956,15 +4956,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
@@ -4974,7 +4970,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5682,14 +5682,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
@@ -5698,7 +5706,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5720,20 +5728,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
@@ -5766,22 +5774,14 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5812,22 +5812,14 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
@@ -5836,7 +5828,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5858,20 +5850,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="J114" t="inlineStr"/>
@@ -5904,14 +5896,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5942,22 +5942,26 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2040.0</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
@@ -5966,7 +5970,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5988,23 +5992,23 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>408.0</t>
+          <t>17952.0</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -6038,26 +6042,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6088,26 +6088,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>17952.0</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -6116,7 +6112,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6138,22 +6134,26 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6184,26 +6184,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
@@ -6212,7 +6208,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6234,22 +6230,26 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6280,30 +6280,22 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>1680.0</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
@@ -6312,7 +6304,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6480,22 +6472,30 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>10.1093</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>10.1093</t>
-        </is>
-      </c>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6526,30 +6526,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
@@ -6558,7 +6550,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6580,20 +6572,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -6626,20 +6618,20 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>51.959</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>51.959</t>
         </is>
       </c>
       <c r="J130" t="inlineStr"/>
@@ -6672,20 +6664,20 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -6718,20 +6710,20 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="J132" t="inlineStr"/>
@@ -6764,22 +6756,30 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6810,20 +6810,20 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J134" t="inlineStr"/>
@@ -6856,20 +6856,20 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
@@ -7752,7 +7752,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -7806,7 +7806,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7976,7 +7976,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8052,7 +8052,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8090,7 +8090,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8128,7 +8128,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -8144,7 +8144,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -8296,7 +8296,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -8394,7 +8394,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -8508,7 +8508,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -8584,11 +8584,15 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
@@ -8598,11 +8602,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8622,15 +8622,11 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
@@ -8640,7 +8636,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr"/>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8736,7 +8736,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -8790,7 +8790,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>朱绶青</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>盛祎</t>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -8992,7 +8992,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>朱绶青</t>
+          <t>盛祎</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -9136,11 +9136,15 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
@@ -9152,7 +9156,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9174,7 +9178,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -9212,15 +9216,11 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
-      </c>
+      <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9254,20 +9254,20 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="J192" t="inlineStr"/>
@@ -9300,18 +9300,22 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>策星银河</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
       <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
@@ -9320,7 +9324,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9342,20 +9346,20 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>策星逐日</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="J194" t="inlineStr"/>
@@ -9388,20 +9392,20 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="J195" t="inlineStr"/>
@@ -9434,22 +9438,18 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9480,20 +9480,20 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="J197" t="inlineStr"/>
@@ -9526,20 +9526,20 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="J198" t="inlineStr"/>
@@ -9572,20 +9572,20 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="J199" t="inlineStr"/>
@@ -10009,7 +10009,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T16:09:12.655063</t>
+          <t>生成时间: 2026-06-12T16:30:01.093216</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/301581_黄山谷捷_三表抽取.xlsx
+++ b/outputs/week2_excel/301581_黄山谷捷_三表抽取.xlsx
@@ -1932,7 +1932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L143"/>
+  <dimension ref="A1:L211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2674,15 +2674,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>深圳市云汉电子有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -2694,7 +2690,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2712,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -2754,11 +2750,15 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3290,15 +3290,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -3332,11 +3328,15 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3826,13 +3826,13 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -3868,15 +3868,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>7412.0</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -3888,7 +3884,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3910,13 +3906,13 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -3952,13 +3948,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1584.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -3994,11 +3990,15 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4032,13 +4032,13 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -4074,13 +4074,13 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -4116,15 +4116,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -4136,7 +4132,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4158,11 +4154,15 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -4272,11 +4272,15 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -4288,7 +4292,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4314,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -4348,15 +4352,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -4682,11 +4682,15 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -4698,7 +4702,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4720,15 +4724,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>1153.0</t>
-        </is>
-      </c>
+      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4762,13 +4762,13 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>10377.0</t>
+          <t>1153.0</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -4804,11 +4804,15 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
@@ -4818,11 +4822,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -4918,15 +4918,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
@@ -4936,7 +4932,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -5017,30 +5017,42 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>6999.972</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>-0.028</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5048,37 +5060,49 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2999.988</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>-0.012</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5086,37 +5110,49 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>1499.994</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>-0.006</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5124,37 +5160,49 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>10000.0027</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>0.0027</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5162,37 +5210,49 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>10000.0027</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>0.0027</t>
+        </is>
+      </c>
       <c r="K101" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5200,37 +5260,49 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>5000.0031</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>0.0031</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5238,37 +5310,49 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>3000.0012</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>0.0012</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5276,37 +5360,49 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2912.5034</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2912.5</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>0.0034</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5314,37 +5410,49 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2000.0019</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>0.0019</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5352,75 +5460,99 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1747.5007</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1747.5</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>0.0007</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>price×shares vs amount diff=0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>999.9993</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5428,37 +5560,49 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>999.9993</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5466,37 +5610,49 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>339.999</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>340.0</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>-0.001</t>
+        </is>
+      </c>
       <c r="K109" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5504,29 +5660,29 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -5549,29 +5705,37 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -5580,36 +5744,44 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -5618,36 +5790,44 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
@@ -5663,22 +5843,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -5701,42 +5881,38 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>盛祎等15名自然人</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>321.5</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>1739.315</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
-          <t>1723.09</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>16.225</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5744,36 +5920,44 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.9%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
@@ -5789,29 +5973,37 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>盛祎</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
@@ -5820,35 +6012,47 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>朱绶青</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
@@ -5865,33 +6069,37 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -5900,35 +6108,47 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>牛威</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
@@ -5938,35 +6158,47 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>吴功友</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2040.0</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
@@ -5976,39 +6208,47 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>牛威(罗永红代持)</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
@@ -6025,33 +6265,37 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>吴功友(王金林代持)</t>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
@@ -6060,42 +6304,42 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -6113,33 +6357,37 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
       <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
@@ -6148,42 +6396,42 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -6201,37 +6449,45 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>策星揽月</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
@@ -6240,44 +6496,52 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>幸福一期</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
@@ -6286,42 +6550,42 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -6339,33 +6603,37 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
       <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
@@ -6374,42 +6642,42 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -6427,37 +6695,45 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
@@ -6466,49 +6742,45 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司 (认缴→存量)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6516,49 +6788,45 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>策星九天 (认缴→存量)</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6566,49 +6834,45 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>幸福一期 (认缴→存量)</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6616,42 +6880,42 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>策星揽月 (认缴→存量)</t>
+          <t>上海泽升贸易有限公司 (认缴→存量)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -6673,35 +6937,35 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>幸福二期 (认缴→存量)</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -6723,35 +6987,35 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>策星银河 (认缴→存量)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -6773,35 +7037,35 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>策星逐日 (认缴→存量)</t>
+          <t>罗世兵 (认缴→存量)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -6820,24 +7084,2932 @@
         </is>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
     <row r="141">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t>认缴流量: 16 条</t>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="3" t="inlineStr">
-        <is>
-          <t>股权存量: 16 条</t>
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>上海骁墨信息技术服务中心(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T17:00:58.787232</t>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>上海联炻企业管理中心(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>安吉璞颉企业管理合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>上海杉创智至创业投资合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>深圳市达晨财智创业投资管理有限公司 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Cheer Rise Consultants Limited</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>黄学英</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>史建伟</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>周乃鼎</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>黄学英/刘鸿雁</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>EARN ACE LIMITED</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>深圳中证投资有限责任公司</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>香港迅雷有限公司</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>北京岚锋创视网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>QM101 Limited</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>厦门富凯海创投资管理有限责任公司</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>QM101 Limited</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>EARN ACE LIMITED</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>香港迅雷有限公司</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>北京岚锋创视网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>QM101 Limited</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>EARN ACE LIMITED</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>香港迅雷有限公司</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>北京岚锋创视网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>盛祎等15名自然人</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>321.5</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>1739.315</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>1723.09</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>16.225</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>price×shares vs amount diff=0.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2002-11-07</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>盛祎</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2002-11-07</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2002-11-07</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>朱绶青</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>四方股份</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>吴功友(王金林代持)</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>牛威</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>吴功友</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>牛威(罗永红代持)</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>策星九天</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>幸福二期</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>策星逐日</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>牛威</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>吴功友</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>中科星图股份有限公司</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>幸福一期</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>策星揽月</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>策星银河</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>中科星图股份有限公司 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>策星九天 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>幸福一期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>策星揽月 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>幸福二期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>策星银河 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>策星逐日 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>认缴流量: 16 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>股权存量: 16 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>生成时间: 2026-06-12T17:05:42.635495</t>
         </is>
       </c>
     </row>
